--- a/examples/leader_smi/02_upd_leader_smi.xlsx
+++ b/examples/leader_smi/02_upd_leader_smi.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Видеоролик на телеканале Россия 1</t>
+          <t>Видеоролик на ТК Россия 1</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -491,19 +491,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Размещение баннера РИА Новости</t>
+          <t>Видеоролик НТВ</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>сутки</t>
+          <t>секунда</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>60000</v>
+        <v>202500</v>
       </c>
     </row>
     <row r="8">
@@ -512,11 +512,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Радиоролик на радиостанции Маяк</t>
+          <t>Видеоролик на Первом канале</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>48000</v>
+        <v>97500</v>
       </c>
     </row>
     <row r="9">
@@ -533,19 +533,460 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Видеоролик на Первом канале</t>
+          <t>Размещение анонса Россия 1 прайм-тайм</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>20</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>секунда</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Спонсорский блок Первый канал открытие</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>выход</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Радиоролик Маяк</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>60</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>секунда</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Радиоролик на Авторадио</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>90</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>секунда</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>67500</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Радиоролик Эхо Москвы</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>45</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>секунда</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>42750</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Спонсорство утреннего шоу Авторадио</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>выход</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Статья в газете Коммерсантъ</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>полоса</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>84000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Статья в журнале Известия</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>полоса</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Модуль 1/2 полосы Известия</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>выход</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>54000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Модуль 1/4 полосы Коммерсантъ</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>выход</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Баннер РИА Новости</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>сутки</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>84000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
         <v>15</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>секунда</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>97500</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Баннер РБК</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>сутки</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>67500</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Баннер на Лента.ру</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>сутки</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>95000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Публикация в Яндекс.Дзен</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>выход</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>34000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Пост в Telegram-канале</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>выход</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Видеореклама на YouTube pre-roll</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>12</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>выход</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>57600</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Билборд 6x3 Москва ТТК</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>95000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ситилайт центр Москвы</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>76000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Размещение на медиафасаде</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>10</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>сутки</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Производство видеоролика 30 сек стандарт</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ролик</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Дизайн баннера интернет</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>макет</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>22500</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Аналитический отчёт по итогам кампании</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>отчёт</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>35000</v>
       </c>
     </row>
   </sheetData>
